--- a/Excel/访客调参表.xlsx
+++ b/Excel/访客调参表.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -548,6 +548,36 @@
       <c r="C7" t="inlineStr">
         <is>
           <t>气泡停留时长（tick）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>needPromptMinTicks</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>60</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>入住后到开口示意的最短间隔（tick）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>needPromptMaxTicks</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>180</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>入住后到开口示意的最长间隔（tick）；服务超时从示意那一刻起算</t>
         </is>
       </c>
     </row>

--- a/Excel/访客调参表.xlsx
+++ b/Excel/访客调参表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="调参" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="氛围访客" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="调参" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="氛围访客" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -65,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -73,6 +73,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -509,37 +510,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bubbleIntervalTicks</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>120</v>
+          <t>actorWorldScale</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0.6</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>闲逛冒泡间隔（tick）</t>
+          <t>访客演员基础世界缩放（叠加透视缩放前）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bubbleJitterTicks</t>
+          <t>bubbleIntervalTicks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>冒泡间隔抖动（tick），实际=间隔±抖动</t>
+          <t>闲逛冒泡间隔（tick）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bubbleHoldTicks</t>
+          <t>bubbleJitterTicks</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -547,35 +548,50 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>气泡停留时长（tick）</t>
+          <t>冒泡间隔抖动（tick），实际=间隔±抖动</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>needPromptMinTicks</t>
+          <t>bubbleHoldTicks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>入住后到开口示意的最短间隔（tick）</t>
+          <t>气泡停留时长（tick）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>needPromptMinTicks</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>60</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>入住后到开口示意的最短间隔（tick）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>needPromptMaxTicks</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B10" t="n">
         <v>180</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>入住后到开口示意的最长间隔（tick）；服务超时从示意那一刻起算</t>
         </is>
